--- a/docs/clinic_management_function_list.xlsx
+++ b/docs/clinic_management_function_list.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Functions'!$A$1:$I$438</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Functions'!$A$1:$I$462</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -726,7 +726,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -735,11 +735,11 @@
         </is>
       </c>
       <c r="F6" s="6" t="n">
-        <v>367</v>
+        <v>382</v>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>84.0%</t>
+          <t>82.9%</t>
         </is>
       </c>
     </row>
@@ -750,11 +750,11 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
@@ -763,11 +763,11 @@
         </is>
       </c>
       <c r="F7" s="6" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>15.0%</t>
         </is>
       </c>
     </row>
@@ -778,11 +778,11 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.2%</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>13.9%</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="B10" s="14" t="n">
-        <v>437</v>
+        <v>461</v>
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
@@ -1781,29 +1781,29 @@
         </is>
       </c>
       <c r="B41" s="6" t="n">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="C41" s="6" t="n">
         <v>9</v>
       </c>
       <c r="D41" s="6" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="E41" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H41" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>20%</t>
         </is>
       </c>
     </row>
@@ -1814,29 +1814,29 @@
         </is>
       </c>
       <c r="B42" s="14" t="n">
-        <v>437</v>
+        <v>461</v>
       </c>
       <c r="C42" s="14" t="n">
         <v>114</v>
       </c>
       <c r="D42" s="14" t="n">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="E42" s="14" t="n">
         <v>64</v>
       </c>
       <c r="F42" s="14" t="n">
-        <v>367</v>
+        <v>382</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="H42" s="14" t="n">
         <v>10</v>
       </c>
       <c r="I42" s="14" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>25%</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I438"/>
+  <dimension ref="A1:I462"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -22522,8 +22522,1136 @@
         </is>
       </c>
     </row>
+    <row r="439">
+      <c r="A439" s="49" t="inlineStr">
+        <is>
+          <t>NFR</t>
+        </is>
+      </c>
+      <c r="B439" s="33" t="inlineStr">
+        <is>
+          <t>NFR-023</t>
+        </is>
+      </c>
+      <c r="C439" s="34" t="inlineStr">
+        <is>
+          <t>Data classification 4-tier</t>
+        </is>
+      </c>
+      <c r="D439" s="35" t="inlineStr">
+        <is>
+          <t>T0 Public · T1 Internal · T2 PII · T3 PHI/Credentials</t>
+        </is>
+      </c>
+      <c r="E439" s="36" t="inlineStr">
+        <is>
+          <t>Mỗi field/column được gán 1 tier T0-T3. T0 Public (an toàn hiển thị, vd tên PK, tên DV); T1 Internal (chỉ user trong tenant, vd note appointment); T2 Confidential PII (định danh cá nhân, vd patient.name/phone/email/address — cần encryption + audit); T3 Restricted (PHI bệnh án + credentials, vd CCCD/BHYT/MFA/diff audit — cần per-row audit + masking + access logging). PII inventory ~30 columns ở T2/T3 trong SECURITY.md §1.1. PR template có checklist xác định tier khi thêm column mới.</t>
+        </is>
+      </c>
+      <c r="F439" s="35" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="G439" s="37" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="H439" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I439" s="39" t="inlineStr">
+        <is>
+          <t>⬜ TODO</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="49" t="inlineStr">
+        <is>
+          <t>NFR</t>
+        </is>
+      </c>
+      <c r="B440" s="33" t="inlineStr">
+        <is>
+          <t>NFR-024</t>
+        </is>
+      </c>
+      <c r="C440" s="34" t="inlineStr">
+        <is>
+          <t>Column-level encryption T3</t>
+        </is>
+      </c>
+      <c r="D440" s="35" t="inlineStr">
+        <is>
+          <t>AES-256 envelope encryption ngoài TDE</t>
+        </is>
+      </c>
+      <c r="E440" s="36" t="inlineStr">
+        <is>
+          <t>Cho các field T3 (CCCD, BHYT card, MFA secret, audit diff): thêm 1 lớp column-level encryption AES-256 trên top TDE. Dùng envelope pattern — mỗi field encrypt với data key (DEK) random, DEK encrypt với master key. Master key trong KMS không bao giờ rời. Lợi ích: tách quyền DBA và security (DBA query thấy ciphertext), per-tenant key isolation (leak 1 clinic không ảnh hưởng clinic khác), audit per-decrypt (KMS log mỗi lần), crypto-shred capability.</t>
+        </is>
+      </c>
+      <c r="F440" s="35" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="G440" s="37" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="H440" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I440" s="39" t="inlineStr">
+        <is>
+          <t>⬜ TODO</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="49" t="inlineStr">
+        <is>
+          <t>NFR</t>
+        </is>
+      </c>
+      <c r="B441" s="33" t="inlineStr">
+        <is>
+          <t>NFR-025</t>
+        </is>
+      </c>
+      <c r="C441" s="34" t="inlineStr">
+        <is>
+          <t>Per-tenant encryption keys</t>
+        </is>
+      </c>
+      <c r="D441" s="35" t="inlineStr">
+        <is>
+          <t>1 master key per clinic trong KMS</t>
+        </is>
+      </c>
+      <c r="E441" s="36" t="inlineStr">
+        <is>
+          <t>Mỗi clinic có 1 master key riêng `clinic:{id}:pii` trong AWS KMS hoặc HashiCorp Vault. Tất cả T2/T3 data của clinic đó encrypt với hierarchy key có root là master này. Leak master key của 1 clinic chỉ ảnh hưởng clinic đó, không cross-tenant. Crypto-shred (revoke master key) → instant data destruction toàn clinic — dùng cho disaster recovery hoặc clinic terminate dịch vụ.</t>
+        </is>
+      </c>
+      <c r="F441" s="35" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="G441" s="37" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="H441" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I441" s="39" t="inlineStr">
+        <is>
+          <t>⬜ TODO</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="49" t="inlineStr">
+        <is>
+          <t>NFR</t>
+        </is>
+      </c>
+      <c r="B442" s="33" t="inlineStr">
+        <is>
+          <t>NFR-026</t>
+        </is>
+      </c>
+      <c r="C442" s="34" t="inlineStr">
+        <is>
+          <t>Key rotation policy</t>
+        </is>
+      </c>
+      <c r="D442" s="35" t="inlineStr">
+        <is>
+          <t>Master 1y · Tenant 1y · JWT 30d · Backup 90d · TLS 90d</t>
+        </is>
+      </c>
+      <c r="E442" s="36" t="inlineStr">
+        <is>
+          <t>Master Key (KMS) rotate tự động 1 năm; Tenant Key 1 năm hoặc on-demand khi nghi ngờ leak; JWT signing key 30 ngày với grace 7d overlap; Backup key 90 ngày (versioned — old backup vẫn dùng key cũ); TLS cert 90 ngày qua Let's Encrypt certbot. Tất cả zero-downtime rotation. Re-encrypt background job cho tenant key rotation.</t>
+        </is>
+      </c>
+      <c r="F442" s="35" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="G442" s="37" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="H442" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I442" s="38" t="inlineStr">
+        <is>
+          <t>🔄 IN_PROGRESS</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="49" t="inlineStr">
+        <is>
+          <t>NFR</t>
+        </is>
+      </c>
+      <c r="B443" s="33" t="inlineStr">
+        <is>
+          <t>NFR-027</t>
+        </is>
+      </c>
+      <c r="C443" s="34" t="inlineStr">
+        <is>
+          <t>Bcrypt cost ≥12</t>
+        </is>
+      </c>
+      <c r="D443" s="35" t="inlineStr">
+        <is>
+          <t>Password hashing factor 12+ thay default 10</t>
+        </is>
+      </c>
+      <c r="E443" s="36" t="inlineStr">
+        <is>
+          <t>Mặc định bcrypt cost 10 không đủ cho hardware 2026+. Tăng lên 12 (4× chậm hơn → 4× tốn chi phí brute force). Pepper toàn cục optional defense in depth. Password history không cho dùng lại 5 password gần nhất, rotation 90 ngày (config được). Min length 12 ký tự + complexity.</t>
+        </is>
+      </c>
+      <c r="F443" s="35" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="G443" s="37" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="H443" s="35" t="inlineStr">
+        <is>
+          <t>TASK-003</t>
+        </is>
+      </c>
+      <c r="I443" s="38" t="inlineStr">
+        <is>
+          <t>🔄 IN_PROGRESS</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="49" t="inlineStr">
+        <is>
+          <t>NFR</t>
+        </is>
+      </c>
+      <c r="B444" s="33" t="inlineStr">
+        <is>
+          <t>NFR-028</t>
+        </is>
+      </c>
+      <c r="C444" s="34" t="inlineStr">
+        <is>
+          <t>JWT RS256 + key rotation</t>
+        </is>
+      </c>
+      <c r="D444" s="35" t="inlineStr">
+        <is>
+          <t>Asymmetric signing thay HS256</t>
+        </is>
+      </c>
+      <c r="E444" s="36" t="inlineStr">
+        <is>
+          <t>Phase 2: chuyển từ HS256 (symmetric, shared secret nguy hiểm) sang RS256 (asymmetric). Public key publish ở /.well-known/jwks.json để service khác verify mà không cần share secret. Key rotation 30 ngày với grace 7d overlap (cả 2 key valid trong giai đoạn chuyển). Phase 1 vẫn HS256 với secret rotation manual.</t>
+        </is>
+      </c>
+      <c r="F444" s="35" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="G444" s="38" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="H444" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I444" s="39" t="inlineStr">
+        <is>
+          <t>⬜ TODO</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="49" t="inlineStr">
+        <is>
+          <t>NFR</t>
+        </is>
+      </c>
+      <c r="B445" s="33" t="inlineStr">
+        <is>
+          <t>NFR-029</t>
+        </is>
+      </c>
+      <c r="C445" s="34" t="inlineStr">
+        <is>
+          <t>Session fingerprinting</t>
+        </is>
+      </c>
+      <c r="D445" s="35" t="inlineStr">
+        <is>
+          <t>Detect device/IP đột ngột đổi</t>
+        </is>
+      </c>
+      <c r="E445" s="36" t="inlineStr">
+        <is>
+          <t>Mỗi JWT issue đính kèm session fingerprint (device ID Tauri uniqueId hoặc browser fp + IP + geo + UA + time). Khi user dùng JWT từ device/IP khác đột ngột → force re-MFA hoặc re-login + alert email 'Phiên đăng nhập từ thiết bị mới [Hà Nội, 14:30]'. Tránh JWT bị steal dùng từ máy attacker.</t>
+        </is>
+      </c>
+      <c r="F445" s="35" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="G445" s="38" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="H445" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I445" s="39" t="inlineStr">
+        <is>
+          <t>⬜ TODO</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="49" t="inlineStr">
+        <is>
+          <t>NFR</t>
+        </is>
+      </c>
+      <c r="B446" s="33" t="inlineStr">
+        <is>
+          <t>NFR-030</t>
+        </is>
+      </c>
+      <c r="C446" s="34" t="inlineStr">
+        <is>
+          <t>PII redaction trong log</t>
+        </is>
+      </c>
+      <c r="D446" s="35" t="inlineStr">
+        <is>
+          <t>structlog không log full PII</t>
+        </is>
+      </c>
+      <c r="E446" s="36" t="inlineStr">
+        <is>
+          <t>Cấm log full PII trong structlog output. Email 'bs.an@hd.vn' → log 'b***@h***.vn'; Phone '0987654321' → '***1234'; CCCD '079123456789' → '***7890'. Pattern `__audit_exclude__: ClassVar[frozenset[str]]` cho models có secret column. Global redact list trong `app/core/audit.py` catch common names. Verify qua log review tool hằng tuần.</t>
+        </is>
+      </c>
+      <c r="F446" s="35" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="G446" s="37" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="H446" s="35" t="inlineStr">
+        <is>
+          <t>TASK-002</t>
+        </is>
+      </c>
+      <c r="I446" s="38" t="inlineStr">
+        <is>
+          <t>🔄 IN_PROGRESS</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="49" t="inlineStr">
+        <is>
+          <t>NFR</t>
+        </is>
+      </c>
+      <c r="B447" s="33" t="inlineStr">
+        <is>
+          <t>NFR-031</t>
+        </is>
+      </c>
+      <c r="C447" s="34" t="inlineStr">
+        <is>
+          <t>Data minimization</t>
+        </is>
+      </c>
+      <c r="D447" s="35" t="inlineStr">
+        <is>
+          <t>Chỉ thu thập field cần thiết</t>
+        </is>
+      </c>
+      <c r="E447" s="36" t="inlineStr">
+        <is>
+          <t>Form đăng ký BN có 2 mode: Quick (chỉ tên + SĐT + DOB + giới — minimal cho walk-in) và Full (thêm CCCD + BHYT + địa chỉ — khi BN có BHYT hoặc khám lần đầu). Tránh PII trong URL query string (dễ leak access log nginx) — chỉ POST body. Không lưu thông tin không dùng đến (vd màu mắt cha mẹ BN nếu không phải nhi khoa).</t>
+        </is>
+      </c>
+      <c r="F447" s="35" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="G447" s="37" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="H447" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I447" s="39" t="inlineStr">
+        <is>
+          <t>⬜ TODO</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="49" t="inlineStr">
+        <is>
+          <t>NFR</t>
+        </is>
+      </c>
+      <c r="B448" s="33" t="inlineStr">
+        <is>
+          <t>NFR-032</t>
+        </is>
+      </c>
+      <c r="C448" s="34" t="inlineStr">
+        <is>
+          <t>Right to Erasure (Nghị định 13)</t>
+        </is>
+      </c>
+      <c r="D448" s="35" t="inlineStr">
+        <is>
+          <t>BN xoá hồ sơ qua crypto-shred</t>
+        </is>
+      </c>
+      <c r="E448" s="36" t="inlineStr">
+        <is>
+          <t>BN yêu cầu xoá data theo Nghị định 13/2023/NĐ-CP. Process: (1) Soft delete row (set deleted_at), (2) Crypto-shred encryption key của BN đó — ciphertext còn nguyên trên disk nhưng forever unreadable, (3) Audit event 'crypto.shred.executed'. Confirm 2 bước (irreversible). Process ≤30 ngày từ khi request (Nghị định bắt buộc).</t>
+        </is>
+      </c>
+      <c r="F448" s="35" t="inlineStr">
+        <is>
+          <t>Patient</t>
+        </is>
+      </c>
+      <c r="G448" s="38" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="H448" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I448" s="39" t="inlineStr">
+        <is>
+          <t>⬜ TODO</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="49" t="inlineStr">
+        <is>
+          <t>NFR</t>
+        </is>
+      </c>
+      <c r="B449" s="33" t="inlineStr">
+        <is>
+          <t>NFR-033</t>
+        </is>
+      </c>
+      <c r="C449" s="34" t="inlineStr">
+        <is>
+          <t>Data portability</t>
+        </is>
+      </c>
+      <c r="D449" s="35" t="inlineStr">
+        <is>
+          <t>BN download data của mình</t>
+        </is>
+      </c>
+      <c r="E449" s="36" t="inlineStr">
+        <is>
+          <t>Quyền theo Nghị định 13 — BN download data của mình dạng JSON + PDF. Self-service portal trong Profile (Phase 2). Encrypted export với password user-provided (AES-256). TTL trên storage 24h. Export bao gồm: thông tin BN, lịch sử khám, chẩn đoán, đơn thuốc, hoá đơn, kết quả CLS.</t>
+        </is>
+      </c>
+      <c r="F449" s="35" t="inlineStr">
+        <is>
+          <t>Patient</t>
+        </is>
+      </c>
+      <c r="G449" s="38" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="H449" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I449" s="39" t="inlineStr">
+        <is>
+          <t>⬜ TODO</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="49" t="inlineStr">
+        <is>
+          <t>NFR</t>
+        </is>
+      </c>
+      <c r="B450" s="33" t="inlineStr">
+        <is>
+          <t>NFR-034</t>
+        </is>
+      </c>
+      <c r="C450" s="34" t="inlineStr">
+        <is>
+          <t>WAF (Web Application Firewall)</t>
+        </is>
+      </c>
+      <c r="D450" s="35" t="inlineStr">
+        <is>
+          <t>Cloudflare/AWS WAF + OWASP ruleset</t>
+        </is>
+      </c>
+      <c r="E450" s="36" t="inlineStr">
+        <is>
+          <t>Cloudflare hoặc AWS WAF với OWASP Top 10 ruleset auto-update. Custom rules: SQL keywords trong query string → block; Bot detection (challenge headless browser unsigned); Geo-block per clinic config (vd PK chỉ phục vụ VN → block IP nước ngoài). Rate limit per endpoint configurable.</t>
+        </is>
+      </c>
+      <c r="F450" s="35" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="G450" s="38" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="H450" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I450" s="39" t="inlineStr">
+        <is>
+          <t>⬜ TODO</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="49" t="inlineStr">
+        <is>
+          <t>NFR</t>
+        </is>
+      </c>
+      <c r="B451" s="33" t="inlineStr">
+        <is>
+          <t>NFR-035</t>
+        </is>
+      </c>
+      <c r="C451" s="34" t="inlineStr">
+        <is>
+          <t>DDoS protection</t>
+        </is>
+      </c>
+      <c r="D451" s="35" t="inlineStr">
+        <is>
+          <t>Cloudflare + circuit breaker + auto-scale</t>
+        </is>
+      </c>
+      <c r="E451" s="36" t="inlineStr">
+        <is>
+          <t>Cloudflare Pro+ với Always Online (serve cache khi origin down). Circuit breaker FastAPI level qua slowapi + tenacity. Auto-scale infrastructure: k8s HPA cho pod (CPU &gt; 70% → scale out), RDS read replica auto-add khi CPU cao. Throttle khi attack detected.</t>
+        </is>
+      </c>
+      <c r="F451" s="35" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="G451" s="38" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="H451" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I451" s="39" t="inlineStr">
+        <is>
+          <t>⬜ TODO</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="49" t="inlineStr">
+        <is>
+          <t>NFR</t>
+        </is>
+      </c>
+      <c r="B452" s="33" t="inlineStr">
+        <is>
+          <t>NFR-036</t>
+        </is>
+      </c>
+      <c r="C452" s="34" t="inlineStr">
+        <is>
+          <t>mTLS internal service-to-service</t>
+        </is>
+      </c>
+      <c r="D452" s="35" t="inlineStr">
+        <is>
+          <t>API ↔ DB ↔ Redis ↔ Worker ↔ S3</t>
+        </is>
+      </c>
+      <c r="E452" s="36" t="inlineStr">
+        <is>
+          <t>Service nội bộ không exposed public dùng mTLS với cert internal CA (HashiCorp Vault). Cert 30 ngày rotate auto. Cert pinning ở client side (verify subject CN). Không dùng password authentication cho DB/Redis ở prod.</t>
+        </is>
+      </c>
+      <c r="F452" s="35" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="G452" s="38" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="H452" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I452" s="39" t="inlineStr">
+        <is>
+          <t>⬜ TODO</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="49" t="inlineStr">
+        <is>
+          <t>NFR</t>
+        </is>
+      </c>
+      <c r="B453" s="33" t="inlineStr">
+        <is>
+          <t>NFR-037</t>
+        </is>
+      </c>
+      <c r="C453" s="34" t="inlineStr">
+        <is>
+          <t>SAST static analysis</t>
+        </is>
+      </c>
+      <c r="D453" s="35" t="inlineStr">
+        <is>
+          <t>ruff + Bandit + ESLint security + Semgrep</t>
+        </is>
+      </c>
+      <c r="E453" s="36" t="inlineStr">
+        <is>
+          <t>ruff (Python lint + security) chạy pre-commit + CI; Bandit (Python SAST) chạy CI block PR nếu high+; ESLint security plugin (TypeScript) pre-commit + CI; Semgrep (multi-lang) chạy CI. Block merge nếu high severity finding.</t>
+        </is>
+      </c>
+      <c r="F453" s="35" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="G453" s="37" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="H453" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I453" s="38" t="inlineStr">
+        <is>
+          <t>🔄 IN_PROGRESS</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="49" t="inlineStr">
+        <is>
+          <t>NFR</t>
+        </is>
+      </c>
+      <c r="B454" s="33" t="inlineStr">
+        <is>
+          <t>NFR-038</t>
+        </is>
+      </c>
+      <c r="C454" s="34" t="inlineStr">
+        <is>
+          <t>DAST dynamic analysis</t>
+        </is>
+      </c>
+      <c r="D454" s="35" t="inlineStr">
+        <is>
+          <t>OWASP ZAP scan pre-prod</t>
+        </is>
+      </c>
+      <c r="E454" s="36" t="inlineStr">
+        <is>
+          <t>OWASP ZAP scan pre-prod env trước mỗi major release. Scope: full crawl + active scan + auth replay. Block release nếu high severity finding. Run weekly scheduled job + on-demand trước release.</t>
+        </is>
+      </c>
+      <c r="F454" s="35" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="G454" s="38" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="H454" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I454" s="39" t="inlineStr">
+        <is>
+          <t>⬜ TODO</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="49" t="inlineStr">
+        <is>
+          <t>NFR</t>
+        </is>
+      </c>
+      <c r="B455" s="33" t="inlineStr">
+        <is>
+          <t>NFR-039</t>
+        </is>
+      </c>
+      <c r="C455" s="34" t="inlineStr">
+        <is>
+          <t>Dependency scanning</t>
+        </is>
+      </c>
+      <c r="D455" s="35" t="inlineStr">
+        <is>
+          <t>Safety + npm audit + Trivy</t>
+        </is>
+      </c>
+      <c r="E455" s="36" t="inlineStr">
+        <is>
+          <t>Safety (Python CVE) + npm audit (Node CVE) + Trivy (container image CVE) chạy CI + nightly. Auto-PR upgrade qua Dependabot/Renovate. Block deploy nếu critical CVE chưa patch ≤7 ngày. SLA: critical 7d, high 30d, medium 90d, low best-effort.</t>
+        </is>
+      </c>
+      <c r="F455" s="35" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="G455" s="37" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="H455" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I455" s="38" t="inlineStr">
+        <is>
+          <t>🔄 IN_PROGRESS</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="49" t="inlineStr">
+        <is>
+          <t>NFR</t>
+        </is>
+      </c>
+      <c r="B456" s="33" t="inlineStr">
+        <is>
+          <t>NFR-040</t>
+        </is>
+      </c>
+      <c r="C456" s="34" t="inlineStr">
+        <is>
+          <t>Secret management</t>
+        </is>
+      </c>
+      <c r="D456" s="35" t="inlineStr">
+        <is>
+          <t>Vault + git-secrets + GitHub scan</t>
+        </is>
+      </c>
+      <c r="E456" s="36" t="inlineStr">
+        <is>
+          <t>Không hardcode secret trong code — git-secrets pre-commit hook + GitHub secret scanning enabled. Dev: .env.local (gitignore). Prod: HashiCorp Vault hoặc AWS Secrets Manager. Tauri config: secrets không bundle, fetch runtime. Frontend không nhận secret nào (chỉ public config qua env build-time prefixed VITE_).</t>
+        </is>
+      </c>
+      <c r="F456" s="35" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="G456" s="37" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="H456" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I456" s="38" t="inlineStr">
+        <is>
+          <t>🔄 IN_PROGRESS</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="49" t="inlineStr">
+        <is>
+          <t>NFR</t>
+        </is>
+      </c>
+      <c r="B457" s="33" t="inlineStr">
+        <is>
+          <t>NFR-041</t>
+        </is>
+      </c>
+      <c r="C457" s="34" t="inlineStr">
+        <is>
+          <t>Backup encryption + ACL</t>
+        </is>
+      </c>
+      <c r="D457" s="35" t="inlineStr">
+        <is>
+          <t>AES-256 + IAM strict + offsite</t>
+        </is>
+      </c>
+      <c r="E457" s="36" t="inlineStr">
+        <is>
+          <t>Backup AES-256 (gpg encrypt) trước khi upload S3 SSE-KMS (double encryption). IAM role chỉ Ops + DBA, MFA-required cho restore. SHA-256 checksum + sign GPG verify integrity khi restore. Cross-region replication HCM → SG. Test restore hằng quý chọn random 1 backup → restore staging → verify data integrity.</t>
+        </is>
+      </c>
+      <c r="F457" s="35" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="G457" s="37" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="H457" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I457" s="39" t="inlineStr">
+        <is>
+          <t>⬜ TODO</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="49" t="inlineStr">
+        <is>
+          <t>NFR</t>
+        </is>
+      </c>
+      <c r="B458" s="33" t="inlineStr">
+        <is>
+          <t>NFR-042</t>
+        </is>
+      </c>
+      <c r="C458" s="34" t="inlineStr">
+        <is>
+          <t>Anomaly detection audit log</t>
+        </is>
+      </c>
+      <c r="D458" s="35" t="inlineStr">
+        <is>
+          <t>Background job 15p quét 7 rules</t>
+        </is>
+      </c>
+      <c r="E458" s="36" t="inlineStr">
+        <is>
+          <t>Arq job chạy mỗi 15 phút quét audit_log với 7 rules: (1) failed_login_burst — ≥10 failed login từ 1 IP trong 5 phút → block IP 1h + alert; (2) mass_pii_reveal — 1 user reveal CCCD ≥30 BN trong 1h → tạm khoá quyền + alert; (3) cross_clinic_access — user truy cập clinic không có pivot → 403 + alert critical; (4) sudden_role_grant — role mới grant + ngay dùng critical perm → force re-MFA; (5) mass_export — ≥100 BN export 1h → tạm dừng export; (6) audit_tamper_detected — hash chain verify fail → lockdown clinic + page on-call; (7) key_decrypt_anomaly — KMS decrypt rate &gt;10× baseline → alert security team.</t>
+        </is>
+      </c>
+      <c r="F458" s="35" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="G458" s="37" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="H458" s="35" t="inlineStr">
+        <is>
+          <t>TASK-002</t>
+        </is>
+      </c>
+      <c r="I458" s="39" t="inlineStr">
+        <is>
+          <t>⬜ TODO</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="49" t="inlineStr">
+        <is>
+          <t>NFR</t>
+        </is>
+      </c>
+      <c r="B459" s="33" t="inlineStr">
+        <is>
+          <t>NFR-043</t>
+        </is>
+      </c>
+      <c r="C459" s="34" t="inlineStr">
+        <is>
+          <t>Breach notification ≤72h</t>
+        </is>
+      </c>
+      <c r="D459" s="35" t="inlineStr">
+        <is>
+          <t>Theo Nghị định 13/2023</t>
+        </is>
+      </c>
+      <c r="E459" s="36" t="inlineStr">
+        <is>
+          <t>Process + template email + DPO contact list. Notify Bộ TTTT trong ≤72 giờ từ khi phát hiện breach. Affected users notify 'không chậm trễ không lý do'. Template email: nature of breach, data affected, mitigation steps, contact DPO. Drill annually để team quen flow. DPO default = VISSoft, custom per clinic Enterprise.</t>
+        </is>
+      </c>
+      <c r="F459" s="35" t="inlineStr">
+        <is>
+          <t>DPO</t>
+        </is>
+      </c>
+      <c r="G459" s="37" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="H459" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I459" s="39" t="inlineStr">
+        <is>
+          <t>⬜ TODO</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="49" t="inlineStr">
+        <is>
+          <t>NFR</t>
+        </is>
+      </c>
+      <c r="B460" s="33" t="inlineStr">
+        <is>
+          <t>NFR-044</t>
+        </is>
+      </c>
+      <c r="C460" s="34" t="inlineStr">
+        <is>
+          <t>Forensic logging + hash chain</t>
+        </is>
+      </c>
+      <c r="D460" s="35" t="inlineStr">
+        <is>
+          <t>Tamper detection trên audit_log</t>
+        </is>
+      </c>
+      <c r="E460" s="36" t="inlineStr">
+        <is>
+          <t>Hash chain trên audit_log: mỗi row có hash = SHA256(prev_hash || row_data). Tampering với row cũ sẽ break chain → detect khi verify. Daily cron verify hash chain. Khi nghi ngờ breach: snapshot DB tại thời điểm phát hiện, preserve raw logs 30 ngày + chain of custody, lock affected accounts (không xoá), document timeline trong incident ticket.</t>
+        </is>
+      </c>
+      <c r="F460" s="35" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="G460" s="37" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="H460" s="35" t="inlineStr">
+        <is>
+          <t>TASK-002</t>
+        </is>
+      </c>
+      <c r="I460" s="39" t="inlineStr">
+        <is>
+          <t>⬜ TODO</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="49" t="inlineStr">
+        <is>
+          <t>NFR</t>
+        </is>
+      </c>
+      <c r="B461" s="33" t="inlineStr">
+        <is>
+          <t>NFR-045</t>
+        </is>
+      </c>
+      <c r="C461" s="34" t="inlineStr">
+        <is>
+          <t>Tauri code signing + secure storage</t>
+        </is>
+      </c>
+      <c r="D461" s="35" t="inlineStr">
+        <is>
+          <t>Win/Mac signing + Tauri Store API</t>
+        </is>
+      </c>
+      <c r="E461" s="36" t="inlineStr">
+        <is>
+          <t>Code signing Win (EV cert) + Mac (notarization Apple) cho Tauri bundle — bắt buộc để OS trust. Update auto-signed via Tauri updater (signature verify trước install). Local storage qua Tauri Store API encrypted (master password derive từ user login session).</t>
+        </is>
+      </c>
+      <c r="F461" s="35" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="G461" s="37" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="H461" s="35" t="inlineStr">
+        <is>
+          <t>TASK-016</t>
+        </is>
+      </c>
+      <c r="I461" s="38" t="inlineStr">
+        <is>
+          <t>🔄 IN_PROGRESS</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="49" t="inlineStr">
+        <is>
+          <t>NFR</t>
+        </is>
+      </c>
+      <c r="B462" s="33" t="inlineStr">
+        <is>
+          <t>NFR-046</t>
+        </is>
+      </c>
+      <c r="C462" s="34" t="inlineStr">
+        <is>
+          <t>Pen test annual</t>
+        </is>
+      </c>
+      <c r="D462" s="35" t="inlineStr">
+        <is>
+          <t>3rd party penetration test mỗi năm</t>
+        </is>
+      </c>
+      <c r="E462" s="36" t="inlineStr">
+        <is>
+          <t>3rd party penetration test mỗi năm 1 lần. Scope: web app + REST API + Tauri client + infrastructure (network, KMS access). Findings tracked trong ticket → fix theo SLA: critical ≤7d, high ≤30d, medium ≤90d. Re-test sau khi fix. Report PDF lưu compliance archive.</t>
+        </is>
+      </c>
+      <c r="F462" s="35" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="G462" s="38" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="H462" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I462" s="39" t="inlineStr">
+        <is>
+          <t>⬜ TODO</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I438"/>
+  <autoFilter ref="A1:I462"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>